--- a/public/kk/downloads/customer-statement.xlsx
+++ b/public/kk/downloads/customer-statement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="How to use" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Statement" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Statement'!$9:$9</definedName>
@@ -575,7 +575,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Statement of account: a template from MDG Services</t>
+          <t>Pump statement of account: a template from MDG Services</t>
         </is>
       </c>
     </row>
@@ -589,28 +589,28 @@
     <row r="4" ht="57" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1. At the top of the Statement sheet, type your business name, the customer's name, the statement date, the period it covers (from and to) and the opening balance.</t>
+          <t>1. At the top of the Statement sheet, type your pump's name, the transporter's name, the statement date, the period it covers (from and to) and the opening balance.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2. Opening balance: what the customer owed you at the start of the period. For a second statement, it is the closing balance of the one before.</t>
+          <t>2. Opening balance: what the transporter owed you at the start of the period. For a second statement, it is the closing balance of the one before.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="74" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>3. One row for every sale and every payment in the period, in date order. Type the date, the bill or slip number, the vehicle or who collected, and the details (item and quantity for a sale; how it was paid and the UTR or cheque number for a payment).</t>
+          <t>3. One row for every credit fill and every payment in the period, in date order. Type the date, the bill or slip number, the truck number, and the details (fuel and litres for a fill; how it was paid and the UTR or cheque number for a payment).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>4. A sale goes in Udhar given (Rs). A payment goes in Money received (Rs). Never both on one row.</t>
+          <t>4. A fill goes in Udhar given (Rs). A payment goes in Money received (Rs). Never both on one row.</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6. The closing balance, at the top and at the foot of the table, is what the customer owes you at the end of the period.</t>
+          <t>6. The closing balance, at the top and at the foot of the table, is what the transporter owes you at the end of the period.</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
     <row r="12" ht="57" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>9. Print it on A4 or save it as a PDF, and send it from your own WhatsApp. Ask the customer to check it and to confirm it or tell you what looks wrong within 7 days.</t>
+          <t>9. Print it on A4 or save it as a PDF, and send it from your own WhatsApp. Ask the transporter to check it and to confirm it or tell you what looks wrong within 7 days.</t>
         </is>
       </c>
     </row>
@@ -677,10 +677,10 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="51" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Khata Kavach, our app, keeps credit sales and payments in one shared book: by default the customer sends a request before goods go out, and both sides see each line as soon as the phone is online. mdgservices.in/khata-kavach</t>
+          <t>Khata Kavach, our app for petrol pumps, keeps every credit fill and payment in one shared book: by default the transporter sends a request before each truck fills, and both sides see each line as soon as the phone is online. mdgservices.in/khata-kavach</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Pump</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Sharma Traders (made-up)</t>
+          <t>Sharma Fuels (made-up)</t>
         </is>
       </c>
       <c r="D4" s="12" t="n"/>
@@ -753,7 +753,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Transporter</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Vehicle no. / collected by</t>
+          <t>Truck no.</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>Details (item and quantity, or how paid and UTR / cheque no.)</t>
+          <t>Details (fuel and litres, or how paid and UTR / cheque no.)</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>UP00 SH 1005</t>
+          <t>UP00 GT 2201</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>Example: diesel, 150 litre</t>
+          <t>Example: diesel, 150 litres</t>
         </is>
       </c>
       <c r="E11" s="23" t="n">
@@ -899,12 +899,12 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>UP00 SH 1006</t>
+          <t>UP00 GT 2202</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>Example: diesel, 200 litre</t>
+          <t>Example: diesel, 200 litres</t>
         </is>
       </c>
       <c r="E12" s="23" t="n">
@@ -1542,12 +1542,12 @@
     <row r="68">
       <c r="A68" s="27" t="inlineStr">
         <is>
-          <t>For the business: sign and date</t>
+          <t>For the pump: sign and date</t>
         </is>
       </c>
       <c r="D68" s="27" t="inlineStr">
         <is>
-          <t>Customer's confirmation: name, sign and date</t>
+          <t>Transporter's confirmation: name, sign and date</t>
         </is>
       </c>
     </row>
